--- a/Testes/reescala/Teste seleção e cruzamento/Teste2/3_melhor_escala.xlsx
+++ b/Testes/reescala/Teste seleção e cruzamento/Teste2/3_melhor_escala.xlsx
@@ -1405,8 +1405,8 @@
       <c r="P8" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" s="4" t="n">
-        <v>1</v>
+      <c r="Q8" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R8" s="5" t="n">
         <v>0</v>
@@ -1738,8 +1738,8 @@
       <c r="P11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q11" s="5" t="n">
-        <v>0</v>
+      <c r="Q11" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R11" s="4" t="n">
         <v>1</v>
@@ -1849,8 +1849,8 @@
       <c r="P12" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" s="4" t="n">
-        <v>1</v>
+      <c r="Q12" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R12" s="5" t="n">
         <v>0</v>
@@ -2191,11 +2191,11 @@
       <c r="S15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" s="4" t="n">
-        <v>1</v>
+      <c r="T15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="V15" s="5" t="n">
         <v>0</v>
@@ -2626,8 +2626,8 @@
       <c r="P19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" s="4" t="n">
-        <v>1</v>
+      <c r="Q19" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R19" s="5" t="n">
         <v>0</v>
@@ -3847,8 +3847,8 @@
       <c r="P30" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q30" s="5" t="n">
-        <v>0</v>
+      <c r="Q30" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R30" s="4" t="n">
         <v>1</v>
@@ -4456,8 +4456,8 @@
       <c r="AH35" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AI35" s="4" t="n">
-        <v>1</v>
+      <c r="AI35" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -4561,14 +4561,14 @@
       <c r="AF36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AG36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI36" s="5" t="n">
-        <v>0</v>
+      <c r="AG36" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -4957,8 +4957,8 @@
       <c r="P40" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" s="5" t="n">
-        <v>0</v>
+      <c r="Q40" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R40" s="4" t="n">
         <v>1</v>
@@ -5068,8 +5068,8 @@
       <c r="P41" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q41" s="5" t="n">
-        <v>0</v>
+      <c r="Q41" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R41" s="5" t="n">
         <v>0</v>
@@ -5857,8 +5857,8 @@
       <c r="T48" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U48" s="5" t="n">
-        <v>0</v>
+      <c r="U48" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="V48" s="5" t="n">
         <v>0</v>
@@ -5896,8 +5896,8 @@
       <c r="AG48" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AH48" s="5" t="n">
-        <v>0</v>
+      <c r="AH48" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AI48" s="5" t="n">
         <v>0</v>
@@ -5956,8 +5956,8 @@
       <c r="P49" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" s="5" t="n">
-        <v>0</v>
+      <c r="Q49" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R49" s="4" t="n">
         <v>1</v>
